--- a/grupos/1BV - Estadisticos 20211.xlsx
+++ b/grupos/1BV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -218,21 +218,21 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Bautista Sarao Eutiquio</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Bautista Sarao Eutiquio</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -278,286 +278,286 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
   </si>
   <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
   </si>
   <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>LEPE</t>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>AMY</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>DANIELA</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
   </si>
   <si>
     <t>SARAHI</t>
@@ -1073,19 +1073,19 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1115,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1150,19 +1150,19 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1195,10 +1195,10 @@
         <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -1227,19 +1227,19 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1272,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1286,13 +1286,13 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>9</v>
@@ -1304,19 +1304,19 @@
         <v>-1</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1340,13 +1340,13 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1372,7 +1372,7 @@
         <v>-1</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1390,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1426,7 +1426,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1458,19 +1458,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1500,10 +1500,10 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1535,19 +1535,19 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1580,10 +1580,10 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1600,10 +1600,10 @@
         <v>-1</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -1612,19 +1612,19 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1654,10 +1654,10 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1680,7 +1680,7 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -1689,7 +1689,7 @@
         <v>-1</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1698,10 +1698,10 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1734,7 +1734,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1748,7 +1748,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>-1</v>
@@ -1766,19 +1766,19 @@
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1811,7 +1811,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1849,13 +1849,13 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1908,10 +1908,10 @@
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -1926,13 +1926,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1962,13 +1962,13 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>-1</v>
@@ -1988,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -2003,13 +2003,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2042,7 +2042,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -2074,19 +2074,19 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2110,16 +2110,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2151,19 +2151,19 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2196,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>7</v>
@@ -2228,19 +2228,19 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2270,10 +2270,10 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2290,13 +2290,13 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -2308,16 +2308,16 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2344,16 +2344,16 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2382,19 +2382,19 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2450,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2459,19 +2459,19 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2495,7 +2495,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2504,7 +2504,7 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2536,19 +2536,19 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2581,7 +2581,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2613,19 +2613,19 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2649,7 +2649,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>8</v>
@@ -2690,19 +2690,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2726,7 +2726,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2735,10 +2735,10 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2767,19 +2767,19 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2809,13 +2809,13 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2844,19 +2844,19 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2880,13 +2880,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2906,7 +2906,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2921,19 +2921,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2960,13 +2960,13 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2986,10 +2986,10 @@
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -3004,13 +3004,13 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3040,10 +3040,10 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3057,7 +3057,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>-1</v>
@@ -3075,7 +3075,7 @@
         <v>-1</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3084,10 +3084,10 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3111,7 +3111,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3120,10 +3120,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>-1</v>
@@ -3152,19 +3152,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3197,10 +3197,10 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3229,19 +3229,19 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3274,7 +3274,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3306,19 +3306,19 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3342,16 +3342,16 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3383,19 +3383,19 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3422,16 +3422,16 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>6</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3445,7 +3445,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>7</v>
@@ -3460,19 +3460,19 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3499,16 +3499,16 @@
         <v>6</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3528,7 +3528,7 @@
         <v>-1</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -3546,10 +3546,10 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3582,7 +3582,7 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>5</v>
@@ -3614,19 +3614,19 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3650,7 +3650,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>10</v>
@@ -3659,7 +3659,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3682,7 +3682,7 @@
         <v>-1</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -3700,10 +3700,10 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3736,7 +3736,7 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3768,19 +3768,19 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3807,13 +3807,13 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>7</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -3836,7 +3836,7 @@
         <v>-1</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F40">
         <v>7</v>
@@ -3854,10 +3854,10 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3890,7 +3890,7 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -3922,19 +3922,19 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3958,13 +3958,13 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U41">
         <v>7</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -3999,7 +3999,7 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -4008,10 +4008,10 @@
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4044,7 +4044,7 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>7</v>
@@ -4076,19 +4076,19 @@
         <v>10</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>-1</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4118,7 +4118,7 @@
         <v>7</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4153,19 +4153,19 @@
         <v>10</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4195,7 +4195,7 @@
         <v>10</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4221,7 +4221,7 @@
         <v>-1</v>
       </c>
       <c r="E45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F45">
         <v>7</v>
@@ -4239,10 +4239,10 @@
         <v>-1</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4275,7 +4275,7 @@
         <v>-1</v>
       </c>
       <c r="W45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X45">
         <v>7</v>
@@ -4298,7 +4298,7 @@
         <v>6</v>
       </c>
       <c r="E46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F46">
         <v>8</v>
@@ -4307,19 +4307,19 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I46">
         <v>-1</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M46">
         <v>-1</v>
@@ -4352,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="W46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X46">
         <v>8</v>
@@ -4375,7 +4375,7 @@
         <v>6</v>
       </c>
       <c r="E47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F47">
         <v>8</v>
@@ -4384,19 +4384,19 @@
         <v>-1</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I47">
         <v>-1</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M47">
         <v>-1</v>
@@ -4429,10 +4429,10 @@
         <v>6</v>
       </c>
       <c r="W47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X47">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y47">
         <v>-1</v>
@@ -4500,30 +4500,30 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>59.09</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>14</v>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4564,25 +4564,25 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4596,30 +4596,30 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>70.45</v>
+        <v>79.55</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4628,30 +4628,30 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>95.45</v>
+      </c>
+      <c r="G6">
+        <v>4.55</v>
+      </c>
+      <c r="H6">
+        <v>8.1</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>70.45</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.1</v>
-      </c>
-      <c r="I6">
-        <v>13</v>
-      </c>
-      <c r="J6">
-        <v>29.55</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -4660,16 +4660,16 @@
         <v>44</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>8.1</v>
@@ -4688,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4723,16 +4723,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4743,16 +4743,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4763,16 +4763,16 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4783,110 +4783,110 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920388</v>
+        <v>21330051920030</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920030</v>
+        <v>21330051920032</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920032</v>
+        <v>21330051920035</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920032</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920032</v>
+        <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4897,159 +4897,159 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920032</v>
+        <v>21330051920036</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920037</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920035</v>
+        <v>21330051920037</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920036</v>
+        <v>21330051920390</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920036</v>
+        <v>21330051920039</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>119</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>67</v>
@@ -5057,99 +5057,99 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920037</v>
+        <v>21330051920039</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920037</v>
+        <v>21330051920039</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920037</v>
+        <v>21330051920043</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
         <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920038</v>
+        <v>21330051920043</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920390</v>
+        <v>21330051920043</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
@@ -5157,99 +5157,99 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920390</v>
+        <v>21330051920045</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920390</v>
+        <v>21330051920048</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
         <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920039</v>
+        <v>21330051920052</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
         <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
         <v>66</v>
@@ -5257,36 +5257,36 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -5297,56 +5297,56 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920043</v>
+        <v>21330051920054</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -5357,36 +5357,36 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
@@ -5397,59 +5397,59 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920045</v>
+        <v>21330051920061</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920045</v>
+        <v>21330051920061</v>
       </c>
       <c r="B38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
         <v>67</v>
@@ -5457,16 +5457,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920048</v>
+        <v>21330051920061</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
         <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -5477,136 +5477,136 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920051</v>
+        <v>21330051920061</v>
       </c>
       <c r="B40" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
         <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920052</v>
+        <v>21330051920067</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920052</v>
+        <v>21330051920067</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -5617,36 +5617,36 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
         <v>5</v>
       </c>
       <c r="F47" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
@@ -5657,36 +5657,36 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920054</v>
+        <v>20330051920185</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
@@ -5697,542 +5697,42 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920057</v>
+        <v>21330051920070</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920057</v>
+        <v>21330051920070</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920057</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920057</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" t="s">
-        <v>84</v>
-      </c>
-      <c r="D54" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920057</v>
-      </c>
-      <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" t="s">
-        <v>84</v>
-      </c>
-      <c r="D55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920059</v>
-      </c>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" t="s">
-        <v>132</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920061</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920061</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" t="s">
-        <v>133</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920061</v>
-      </c>
-      <c r="B59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920061</v>
-      </c>
-      <c r="B60" t="s">
-        <v>92</v>
-      </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E60" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920061</v>
-      </c>
-      <c r="B61" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" t="s">
-        <v>110</v>
-      </c>
-      <c r="D61" t="s">
-        <v>133</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920062</v>
-      </c>
-      <c r="B62" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920062</v>
-      </c>
-      <c r="B63" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" t="s">
-        <v>134</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920062</v>
-      </c>
-      <c r="B64" t="s">
-        <v>93</v>
-      </c>
-      <c r="C64" t="s">
-        <v>90</v>
-      </c>
-      <c r="D64" t="s">
-        <v>134</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920062</v>
-      </c>
-      <c r="B65" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" t="s">
-        <v>90</v>
-      </c>
-      <c r="D65" t="s">
-        <v>134</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920067</v>
-      </c>
-      <c r="B66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C66" t="s">
-        <v>111</v>
-      </c>
-      <c r="D66" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920067</v>
-      </c>
-      <c r="B67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C67" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" t="s">
-        <v>135</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920069</v>
-      </c>
-      <c r="B68" t="s">
-        <v>95</v>
-      </c>
-      <c r="C68" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920069</v>
-      </c>
-      <c r="B69" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920069</v>
-      </c>
-      <c r="B70" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" t="s">
-        <v>112</v>
-      </c>
-      <c r="D70" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920069</v>
-      </c>
-      <c r="B71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" t="s">
-        <v>112</v>
-      </c>
-      <c r="D71" t="s">
-        <v>136</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920069</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" t="s">
-        <v>136</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920185</v>
-      </c>
-      <c r="B73" t="s">
-        <v>96</v>
-      </c>
-      <c r="C73" t="s">
-        <v>113</v>
-      </c>
-      <c r="D73" t="s">
-        <v>137</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920185</v>
-      </c>
-      <c r="B74" t="s">
-        <v>96</v>
-      </c>
-      <c r="C74" t="s">
-        <v>113</v>
-      </c>
-      <c r="D74" t="s">
-        <v>137</v>
-      </c>
-      <c r="E74" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920070</v>
-      </c>
-      <c r="B75" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
-        <v>138</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920070</v>
-      </c>
-      <c r="B76" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
-        <v>138</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920070</v>
-      </c>
-      <c r="B77" t="s">
-        <v>97</v>
-      </c>
-      <c r="C77" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" t="s">
-        <v>138</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6274,316 +5774,316 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920390</v>
+        <v>21330051920057</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920043</v>
+        <v>21330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920052</v>
+        <v>21330051920069</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920057</v>
+        <v>21330051920036</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920061</v>
+        <v>21330051920390</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920069</v>
+        <v>21330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920032</v>
+        <v>21330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920036</v>
+        <v>21330051920052</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920053</v>
+        <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920062</v>
+        <v>21330051920037</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920035</v>
+        <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920037</v>
+        <v>21330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920070</v>
+        <v>21330051920030</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920045</v>
+        <v>21330051920032</v>
       </c>
       <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
         <v>84</v>
       </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920067</v>
+        <v>21330051920035</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920185</v>
+        <v>21330051920038</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920030</v>
+        <v>21330051920045</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6591,16 +6091,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920038</v>
+        <v>21330051920048</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6608,16 +6108,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -6625,16 +6125,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920051</v>
+        <v>20330051920185</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -6642,47 +6142,47 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920054</v>
+        <v>21330051920029</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920059</v>
+        <v>21330051920031</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920029</v>
+        <v>21330051920033</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
@@ -6693,13 +6193,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920031</v>
+        <v>21330051920034</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
         <v>166</v>
@@ -6710,13 +6210,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920033</v>
+        <v>21330051920040</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
         <v>167</v>
@@ -6727,13 +6227,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920034</v>
+        <v>21330051920041</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
         <v>168</v>
@@ -6744,10 +6244,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920040</v>
+        <v>21330051920042</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
         <v>152</v>
@@ -6761,13 +6261,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920041</v>
+        <v>21330051920044</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
         <v>170</v>
@@ -6778,13 +6278,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920042</v>
+        <v>21330051920046</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -6795,13 +6295,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920044</v>
+        <v>21330051920047</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -6812,13 +6312,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920046</v>
+        <v>21330051920050</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -6829,13 +6329,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920047</v>
+        <v>21330051920049</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -6846,13 +6346,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920050</v>
+        <v>21330051920051</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -6863,13 +6363,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920049</v>
+        <v>21330051920055</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -6880,13 +6380,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920055</v>
+        <v>21330051920056</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -6897,13 +6397,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920056</v>
+        <v>21330051920058</v>
       </c>
       <c r="B39" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6914,13 +6414,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920058</v>
+        <v>21330051920059</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6934,10 +6434,10 @@
         <v>21330051920060</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -6951,10 +6451,10 @@
         <v>21330051920063</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -6968,7 +6468,7 @@
         <v>21330051920064</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
         <v>82</v>
@@ -6985,10 +6485,10 @@
         <v>21330051920065</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -7002,13 +6502,13 @@
         <v>21330051920066</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7021,7 +6521,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7053,22 +6553,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920045</v>
+        <v>21330051920037</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -7076,22 +6576,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920045</v>
+        <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -7102,13 +6602,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7125,13 +6625,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -7145,16 +6645,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920185</v>
+        <v>21330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7168,19 +6668,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920185</v>
+        <v>21330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
@@ -7200,7 +6700,7 @@
         <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7214,22 +6714,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920038</v>
+        <v>21330051920032</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -7237,16 +6737,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920048</v>
+        <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7260,22 +6760,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920051</v>
+        <v>21330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -7283,22 +6783,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920054</v>
+        <v>21330051920045</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -7306,16 +6806,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920059</v>
+        <v>21330051920048</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -7324,6 +6824,52 @@
         <v>65</v>
       </c>
       <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920054</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920185</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20211.xlsx
+++ b/grupos/1BV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -218,12 +218,12 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -251,268 +251,268 @@
     <t>ALVARADO</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>AQUINO</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
   </si>
   <si>
     <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
   </si>
   <si>
     <t>GUADALUPE JOSELYNE</t>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1278,7 +1278,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1301,7 +1301,7 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1319,7 +1319,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1355,7 +1355,7 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1473,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1550,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1627,7 +1627,7 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1663,7 +1663,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1917,7 +1917,7 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1935,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1971,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2089,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2243,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2320,7 +2320,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2356,7 +2356,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2397,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2551,7 +2551,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2628,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2664,7 +2664,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2705,7 +2705,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2741,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2782,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2818,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2859,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -3244,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3280,7 +3280,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3321,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3475,7 +3475,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3534,7 +3534,7 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3588,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3629,7 +3629,7 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3783,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3819,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3937,7 +3937,7 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -4014,7 +4014,7 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4050,7 +4050,7 @@
         <v>7</v>
       </c>
       <c r="Y42">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4091,7 +4091,7 @@
         <v>10</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4127,7 +4127,7 @@
         <v>10</v>
       </c>
       <c r="Y43">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4168,7 +4168,7 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4204,7 +4204,7 @@
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4322,7 +4322,7 @@
         <v>7</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4532,30 +4532,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>31.82</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -4688,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4723,10 +4723,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4743,16 +4743,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4763,10 +4763,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4783,16 +4783,16 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4803,10 +4803,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4817,42 +4817,42 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920032</v>
+        <v>21330051920035</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920035</v>
+        <v>21330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4860,19 +4860,19 @@
         <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4880,24 +4880,24 @@
         <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B11" t="s">
         <v>79</v>
@@ -4906,13 +4906,13 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4920,24 +4920,24 @@
         <v>21330051920037</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920037</v>
+        <v>21330051920038</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
@@ -4946,10 +4946,10 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>66</v>
@@ -4957,7 +4957,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920038</v>
+        <v>21330051920390</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
@@ -4966,13 +4966,13 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4980,59 +4980,59 @@
         <v>21330051920390</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920390</v>
+        <v>21330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920390</v>
+        <v>21330051920039</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5040,16 +5040,16 @@
         <v>21330051920039</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>67</v>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920039</v>
+        <v>21330051920043</v>
       </c>
       <c r="B19" t="s">
         <v>82</v>
@@ -5066,18 +5066,18 @@
         <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920039</v>
+        <v>21330051920043</v>
       </c>
       <c r="B20" t="s">
         <v>82</v>
@@ -5086,10 +5086,10 @@
         <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920043</v>
+        <v>21330051920045</v>
       </c>
       <c r="B21" t="s">
         <v>83</v>
@@ -5106,50 +5106,50 @@
         <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920043</v>
+        <v>21330051920048</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920043</v>
+        <v>21330051920052</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>66</v>
@@ -5157,76 +5157,76 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920045</v>
+        <v>21330051920052</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
         <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920048</v>
+        <v>21330051920052</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B26" t="s">
         <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B27" t="s">
         <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -5237,79 +5237,79 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B28" t="s">
         <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B29" t="s">
         <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920053</v>
+        <v>21330051920057</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
         <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920053</v>
+        <v>21330051920057</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D31" t="s">
         <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
         <v>66</v>
@@ -5317,16 +5317,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B32" t="s">
         <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -5337,16 +5337,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B33" t="s">
         <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -5357,36 +5357,36 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B34" t="s">
         <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B35" t="s">
         <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
@@ -5397,36 +5397,36 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B36" t="s">
         <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B37" t="s">
         <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -5437,36 +5437,36 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B38" t="s">
         <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B39" t="s">
         <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920061</v>
+        <v>21330051920067</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
         <v>106</v>
@@ -5489,75 +5489,75 @@
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B41" t="s">
         <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920062</v>
+        <v>21330051920069</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920062</v>
+        <v>21330051920069</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
         <v>128</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B44" t="s">
         <v>92</v>
@@ -5566,18 +5566,18 @@
         <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B45" t="s">
         <v>92</v>
@@ -5586,18 +5586,18 @@
         <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920069</v>
+        <v>20330051920185</v>
       </c>
       <c r="B46" t="s">
         <v>93</v>
@@ -5606,133 +5606,53 @@
         <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
         <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D48" t="s">
         <v>130</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920069</v>
-      </c>
-      <c r="B49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920185</v>
-      </c>
-      <c r="B50" t="s">
-        <v>94</v>
-      </c>
-      <c r="C50" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E50" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920070</v>
-      </c>
-      <c r="B51" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" t="s">
-        <v>132</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920070</v>
-      </c>
-      <c r="B52" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" t="s">
-        <v>110</v>
-      </c>
-      <c r="D52" t="s">
-        <v>132</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5774,10 +5694,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5785,16 +5705,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B3" t="s">
         <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5802,16 +5722,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920061</v>
+        <v>21330051920069</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5819,33 +5739,33 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920069</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920036</v>
+        <v>21330051920039</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5853,16 +5773,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5870,16 +5790,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5887,16 +5807,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
         <v>83</v>
       </c>
-      <c r="C9" t="s">
-        <v>102</v>
-      </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5904,16 +5824,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5921,50 +5841,50 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920053</v>
+        <v>21330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920390</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920037</v>
+        <v>21330051920043</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5975,13 +5895,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5992,13 +5912,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -6012,10 +5932,10 @@
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -6023,16 +5943,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920032</v>
+        <v>21330051920035</v>
       </c>
       <c r="B17" t="s">
         <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6040,16 +5960,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6057,16 +5977,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920038</v>
+        <v>21330051920045</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -6074,7 +5994,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920045</v>
+        <v>21330051920048</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
@@ -6083,7 +6003,7 @@
         <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6091,16 +6011,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6108,16 +6028,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920054</v>
+        <v>20330051920185</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -6125,30 +6045,30 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920185</v>
+        <v>21330051920029</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920029</v>
+        <v>21330051920031</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
         <v>163</v>
@@ -6159,13 +6079,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920031</v>
+        <v>21330051920032</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
         <v>164</v>
@@ -6179,10 +6099,10 @@
         <v>21330051920033</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
@@ -6196,10 +6116,10 @@
         <v>21330051920034</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
         <v>166</v>
@@ -6213,10 +6133,10 @@
         <v>21330051920040</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
         <v>167</v>
@@ -6230,10 +6150,10 @@
         <v>21330051920041</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
         <v>168</v>
@@ -6247,10 +6167,10 @@
         <v>21330051920042</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
         <v>169</v>
@@ -6264,10 +6184,10 @@
         <v>21330051920044</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" t="s">
         <v>170</v>
@@ -6281,10 +6201,10 @@
         <v>21330051920046</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -6298,10 +6218,10 @@
         <v>21330051920047</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -6315,10 +6235,10 @@
         <v>21330051920050</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -6332,10 +6252,10 @@
         <v>21330051920049</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -6349,10 +6269,10 @@
         <v>21330051920051</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -6366,10 +6286,10 @@
         <v>21330051920055</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -6383,10 +6303,10 @@
         <v>21330051920056</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -6400,10 +6320,10 @@
         <v>21330051920058</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6417,10 +6337,10 @@
         <v>21330051920059</v>
       </c>
       <c r="B40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6434,10 +6354,10 @@
         <v>21330051920060</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -6451,10 +6371,10 @@
         <v>21330051920063</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -6468,10 +6388,10 @@
         <v>21330051920064</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -6485,10 +6405,10 @@
         <v>21330051920065</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
         <v>183</v>
@@ -6502,10 +6422,10 @@
         <v>21330051920066</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
         <v>179</v>
@@ -6521,7 +6441,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6556,13 +6476,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6579,19 +6499,19 @@
         <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6599,22 +6519,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920067</v>
+        <v>21330051920390</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6622,22 +6542,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920067</v>
+        <v>21330051920390</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6645,22 +6565,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920070</v>
+        <v>21330051920043</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6668,22 +6588,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920070</v>
+        <v>21330051920043</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6691,16 +6611,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920030</v>
+        <v>21330051920067</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6714,22 +6634,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920032</v>
+        <v>21330051920067</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -6737,16 +6657,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920035</v>
+        <v>21330051920070</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6760,19 +6680,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920038</v>
+        <v>21330051920070</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>67</v>
@@ -6783,22 +6703,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920045</v>
+        <v>21330051920030</v>
       </c>
       <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
         <v>84</v>
       </c>
-      <c r="C12" t="s">
-        <v>103</v>
-      </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6806,16 +6726,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920048</v>
+        <v>21330051920035</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6829,22 +6749,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920054</v>
+        <v>21330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6852,24 +6772,93 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>21330051920045</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920048</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920054</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>20330051920185</v>
       </c>
-      <c r="B15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
         <v>65</v>
       </c>
-      <c r="G15">
+      <c r="G18">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20211.xlsx
+++ b/grupos/1BV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -272,42 +272,42 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -329,214 +329,214 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>PAOLA JAZMIN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
   </si>
   <si>
     <t>MICHEL</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>PAOLA JAZMIN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
   </si>
   <si>
     <t>OSCAR</t>
@@ -2675,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2729,7 +2729,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -4500,25 +4500,25 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>59.09</v>
+        <v>61.36</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>40.91</v>
+        <v>38.64</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4688,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4723,10 +4723,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4743,10 +4743,10 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4763,10 +4763,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4783,10 +4783,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4803,10 +4803,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4826,7 +4826,7 @@
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -4846,7 +4846,7 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4866,7 +4866,7 @@
         <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4886,7 +4886,7 @@
         <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4906,7 +4906,7 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4926,7 +4926,7 @@
         <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -4946,7 +4946,7 @@
         <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -4966,7 +4966,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -4986,7 +4986,7 @@
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -5006,7 +5006,7 @@
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -5026,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -5046,7 +5046,7 @@
         <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -5066,7 +5066,7 @@
         <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -5086,7 +5086,7 @@
         <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -5106,7 +5106,7 @@
         <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -5117,22 +5117,22 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920048</v>
+        <v>21330051920052</v>
       </c>
       <c r="B22" t="s">
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5140,19 +5140,19 @@
         <v>21330051920052</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
         <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5160,39 +5160,39 @@
         <v>21330051920052</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
         <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B25" t="s">
         <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5200,19 +5200,19 @@
         <v>21330051920053</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5220,59 +5220,59 @@
         <v>21330051920053</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B28" t="s">
         <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B29" t="s">
         <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -5280,19 +5280,19 @@
         <v>21330051920057</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
         <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -5300,39 +5300,39 @@
         <v>21330051920057</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
         <v>83</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B32" t="s">
         <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -5340,19 +5340,19 @@
         <v>21330051920061</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5360,19 +5360,19 @@
         <v>21330051920061</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5380,39 +5380,39 @@
         <v>21330051920061</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B36" t="s">
         <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5420,19 +5420,19 @@
         <v>21330051920062</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -5440,39 +5440,39 @@
         <v>21330051920062</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B39" t="s">
         <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -5480,24 +5480,24 @@
         <v>21330051920067</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B41" t="s">
         <v>91</v>
@@ -5506,13 +5506,13 @@
         <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -5520,19 +5520,19 @@
         <v>21330051920069</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5540,19 +5540,19 @@
         <v>21330051920069</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -5560,24 +5560,24 @@
         <v>21330051920069</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920069</v>
+        <v>20330051920185</v>
       </c>
       <c r="B45" t="s">
         <v>92</v>
@@ -5586,18 +5586,18 @@
         <v>107</v>
       </c>
       <c r="D45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920185</v>
+        <v>21330051920070</v>
       </c>
       <c r="B46" t="s">
         <v>93</v>
@@ -5606,7 +5606,7 @@
         <v>108</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
         <v>6</v>
@@ -5620,38 +5620,18 @@
         <v>21330051920070</v>
       </c>
       <c r="B47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E47" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920070</v>
-      </c>
-      <c r="B48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5694,10 +5674,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5708,13 +5688,13 @@
         <v>21330051920061</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5725,13 +5705,13 @@
         <v>21330051920069</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5748,7 +5728,7 @@
         <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5765,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5776,13 +5756,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5793,13 +5773,13 @@
         <v>21330051920053</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5810,13 +5790,13 @@
         <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5827,13 +5807,13 @@
         <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5850,7 +5830,7 @@
         <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5867,7 +5847,7 @@
         <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5884,7 +5864,7 @@
         <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5895,13 +5875,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5912,13 +5892,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -5932,10 +5912,10 @@
         <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5952,7 +5932,7 @@
         <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5969,7 +5949,7 @@
         <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5986,7 +5966,7 @@
         <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5994,16 +5974,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
         <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -6011,16 +5991,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920054</v>
+        <v>20330051920185</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -6028,30 +6008,30 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920185</v>
+        <v>21330051920029</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920029</v>
+        <v>21330051920031</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
         <v>162</v>
@@ -6062,13 +6042,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920031</v>
+        <v>21330051920032</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
         <v>163</v>
@@ -6079,13 +6059,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920032</v>
+        <v>21330051920033</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
         <v>164</v>
@@ -6096,13 +6076,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920033</v>
+        <v>21330051920034</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
@@ -6113,13 +6093,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920034</v>
+        <v>21330051920040</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D27" t="s">
         <v>166</v>
@@ -6130,13 +6110,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920040</v>
+        <v>21330051920041</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>167</v>
@@ -6147,13 +6127,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920041</v>
+        <v>21330051920042</v>
       </c>
       <c r="B29" t="s">
         <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>168</v>
@@ -6164,13 +6144,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920042</v>
+        <v>21330051920044</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
         <v>169</v>
@@ -6181,13 +6161,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920044</v>
+        <v>21330051920046</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
         <v>170</v>
@@ -6198,13 +6178,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920046</v>
+        <v>21330051920047</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -6215,13 +6195,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920047</v>
+        <v>21330051920048</v>
       </c>
       <c r="B33" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -6235,10 +6215,10 @@
         <v>21330051920050</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -6252,10 +6232,10 @@
         <v>21330051920049</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -6269,10 +6249,10 @@
         <v>21330051920051</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -6286,10 +6266,10 @@
         <v>21330051920055</v>
       </c>
       <c r="B37" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -6303,10 +6283,10 @@
         <v>21330051920056</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -6320,7 +6300,7 @@
         <v>21330051920058</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
         <v>83</v>
@@ -6337,10 +6317,10 @@
         <v>21330051920059</v>
       </c>
       <c r="B40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6354,10 +6334,10 @@
         <v>21330051920060</v>
       </c>
       <c r="B41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D41" t="s">
         <v>180</v>
@@ -6371,10 +6351,10 @@
         <v>21330051920063</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
         <v>181</v>
@@ -6388,7 +6368,7 @@
         <v>21330051920064</v>
       </c>
       <c r="B43" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
         <v>81</v>
@@ -6405,7 +6385,7 @@
         <v>21330051920065</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
         <v>102</v>
@@ -6422,10 +6402,10 @@
         <v>21330051920066</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
         <v>179</v>
@@ -6441,7 +6421,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6482,7 +6462,7 @@
         <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6505,7 +6485,7 @@
         <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6528,7 +6508,7 @@
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6551,7 +6531,7 @@
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6574,7 +6554,7 @@
         <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6597,7 +6577,7 @@
         <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -6614,13 +6594,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6637,13 +6617,13 @@
         <v>21330051920067</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -6660,13 +6640,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6683,13 +6663,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -6709,10 +6689,10 @@
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6735,7 +6715,7 @@
         <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -6758,7 +6738,7 @@
         <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -6781,7 +6761,7 @@
         <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -6795,16 +6775,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
         <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6818,16 +6798,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920054</v>
+        <v>20330051920185</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -6836,29 +6816,6 @@
         <v>65</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920185</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1BV - Estadisticos 20211.xlsx
+++ b/grupos/1BV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="184">
   <si>
     <t>Materia</t>
   </si>
@@ -218,21 +218,21 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -248,9 +248,24 @@
     <t>ARAGON</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>ALVARADO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CIRUELO</t>
   </si>
   <si>
@@ -266,12 +281,33 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -281,15 +317,36 @@
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
     <t>TLAXCALTECALT</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -305,7 +362,13 @@
     <t>BRUNO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -323,24 +386,57 @@
     <t>ESTRADA</t>
   </si>
   <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>LEPE</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
     <t>RANGEL</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>YOPIHUA</t>
   </si>
   <si>
@@ -350,9 +446,24 @@
     <t>JONATHAN YOSEF</t>
   </si>
   <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
     <t>PATRICIA</t>
   </si>
   <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
     <t>GABRIELA ELIZABETH</t>
   </si>
   <si>
@@ -371,12 +482,42 @@
     <t>LAURA FERNANDA</t>
   </si>
   <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>NOHEMI</t>
+  </si>
+  <si>
     <t>EMMANUEL DAVID</t>
   </si>
   <si>
+    <t>ARANZA DANAE</t>
+  </si>
+  <si>
     <t>ZURY BETZABE</t>
   </si>
   <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
     <t>DAIRA</t>
   </si>
   <si>
@@ -386,15 +527,39 @@
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
     <t>DARINKA PAOLA</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
   </si>
   <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ANIELKA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
     <t>HANIA ZARETH</t>
   </si>
   <si>
@@ -405,171 +570,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>ANIELKA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -1088,25 +1088,25 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -1124,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1135,7 +1135,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -1153,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1165,31 +1165,31 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1230,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -1245,37 +1245,37 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1322,22 +1322,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1363,13 +1363,13 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -1378,16 +1378,16 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -1396,43 +1396,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1476,22 +1476,22 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1538,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>8</v>
@@ -1553,37 +1553,37 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1597,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1630,34 +1630,34 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1674,10 +1674,10 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1686,16 +1686,16 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1704,34 +1704,34 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1740,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1751,7 +1751,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>6</v>
@@ -1763,13 +1763,13 @@
         <v>7</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H13">
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -1781,31 +1781,31 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1817,7 +1817,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1825,7 +1825,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1843,10 +1843,10 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>6</v>
@@ -1858,28 +1858,28 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1894,7 +1894,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1902,10 +1902,10 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1920,10 +1920,10 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1938,28 +1938,28 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1979,10 +1979,10 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>6</v>
@@ -1994,13 +1994,13 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -2012,31 +2012,31 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2092,22 +2092,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2116,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2154,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2166,34 +2166,34 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>7</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2246,31 +2246,31 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2287,13 +2287,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2305,13 +2305,13 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -2323,34 +2323,34 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2400,31 +2400,31 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2456,13 +2456,13 @@
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H22">
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>6</v>
@@ -2474,28 +2474,28 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2504,13 +2504,13 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2539,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>6</v>
@@ -2554,28 +2554,28 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>7</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2631,22 +2631,22 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2708,28 +2708,28 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2741,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2770,7 +2770,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2785,22 +2785,22 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>7</v>
@@ -2809,7 +2809,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2818,7 +2818,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2862,22 +2862,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2924,7 +2924,7 @@
         <v>6</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2936,28 +2936,28 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2972,7 +2972,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2980,10 +2980,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -2995,13 +2995,13 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -3013,31 +3013,31 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -3049,7 +3049,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3060,10 +3060,10 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3072,16 +3072,16 @@
         <v>9</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H30">
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -3090,34 +3090,34 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3126,7 +3126,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3137,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -3155,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -3167,31 +3167,31 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3203,7 +3203,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3247,22 +3247,22 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3309,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>8</v>
@@ -3324,22 +3324,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3389,7 +3389,7 @@
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -3398,25 +3398,25 @@
         <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3434,7 +3434,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3478,40 +3478,40 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3519,13 +3519,13 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -3537,13 +3537,13 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -3552,40 +3552,40 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>6</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3632,22 +3632,22 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3673,13 +3673,13 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -3688,16 +3688,16 @@
         <v>7</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>6</v>
@@ -3706,43 +3706,43 @@
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>6</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3786,22 +3786,22 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3819,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3827,13 +3827,13 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -3845,13 +3845,13 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -3860,43 +3860,43 @@
         <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3940,22 +3940,22 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -3964,7 +3964,7 @@
         <v>7</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -3984,10 +3984,10 @@
         <v>7</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>8</v>
@@ -4002,10 +4002,10 @@
         <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
         <v>10</v>
@@ -4017,31 +4017,31 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>9</v>
@@ -4050,7 +4050,7 @@
         <v>7</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4079,7 +4079,7 @@
         <v>7</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>8</v>
@@ -4094,31 +4094,31 @@
         <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>7</v>
       </c>
       <c r="U43">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4127,7 +4127,7 @@
         <v>10</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4171,22 +4171,22 @@
         <v>8</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>6</v>
@@ -4198,13 +4198,13 @@
         <v>8</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>10</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4212,13 +4212,13 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>6</v>
@@ -4227,16 +4227,16 @@
         <v>7</v>
       </c>
       <c r="G45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>6</v>
@@ -4245,34 +4245,34 @@
         <v>7</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W45">
         <v>6</v>
@@ -4281,7 +4281,7 @@
         <v>7</v>
       </c>
       <c r="Y45">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4292,7 +4292,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>6</v>
@@ -4310,7 +4310,7 @@
         <v>6</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J46">
         <v>6</v>
@@ -4325,40 +4325,40 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T46">
         <v>6</v>
       </c>
       <c r="U46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V46">
         <v>6</v>
       </c>
       <c r="W46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y46">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:25">
@@ -4369,7 +4369,7 @@
         <v>6</v>
       </c>
       <c r="C47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>6</v>
@@ -4381,13 +4381,13 @@
         <v>8</v>
       </c>
       <c r="G47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H47">
         <v>6</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J47">
         <v>6</v>
@@ -4399,43 +4399,43 @@
         <v>6</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T47">
         <v>6</v>
       </c>
       <c r="U47">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V47">
         <v>6</v>
       </c>
       <c r="W47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X47">
         <v>7</v>
       </c>
       <c r="Y47">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4500,30 +4500,30 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>61.36</v>
+        <v>79.55</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>20.45</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>38.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -4532,30 +4532,30 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>77.27</v>
+        <v>86.36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>13.64</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -4564,30 +4564,30 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -4596,30 +4596,30 @@
         <v>44</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>79.55</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>20.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -4628,19 +4628,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -4672,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4688,7 +4688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4713,926 +4713,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920388</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920388</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920388</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920388</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920030</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920035</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920036</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920036</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920036</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920037</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920037</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920038</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920390</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920390</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920039</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>116</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920039</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920039</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920043</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920043</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920045</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920052</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>96</v>
-      </c>
-      <c r="D22" t="s">
-        <v>119</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920052</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920052</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920053</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920053</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920053</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920054</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920057</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920057</v>
-      </c>
-      <c r="B30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920057</v>
-      </c>
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920061</v>
-      </c>
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920061</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920061</v>
-      </c>
-      <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920061</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920062</v>
-      </c>
-      <c r="B36" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920062</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920062</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920067</v>
-      </c>
-      <c r="B39" t="s">
-        <v>90</v>
-      </c>
-      <c r="C39" t="s">
-        <v>105</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920067</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920069</v>
-      </c>
-      <c r="B41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920069</v>
-      </c>
-      <c r="B42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C42" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920069</v>
-      </c>
-      <c r="B43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D43" t="s">
-        <v>126</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920069</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920185</v>
-      </c>
-      <c r="B45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920070</v>
-      </c>
-      <c r="B46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920070</v>
-      </c>
-      <c r="B47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" t="s">
-        <v>108</v>
-      </c>
-      <c r="D47" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5674,149 +4754,149 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920061</v>
+        <v>21330051920029</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920069</v>
+        <v>21330051920030</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920039</v>
+        <v>21330051920032</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920052</v>
+        <v>21330051920033</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920053</v>
+        <v>21330051920034</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920057</v>
+        <v>21330051920035</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920062</v>
+        <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5824,197 +4904,197 @@
         <v>21330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920390</v>
+        <v>21330051920038</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920043</v>
+        <v>21330051920390</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920067</v>
+        <v>21330051920039</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920070</v>
+        <v>21330051920040</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
         <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920030</v>
+        <v>21330051920041</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920035</v>
+        <v>21330051920042</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920038</v>
+        <v>21330051920043</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920045</v>
+        <v>21330051920044</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920054</v>
+        <v>21330051920045</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920185</v>
+        <v>21330051920046</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920029</v>
+        <v>21330051920047</v>
       </c>
       <c r="B22" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
         <v>161</v>
@@ -6025,13 +5105,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920031</v>
+        <v>21330051920048</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
         <v>162</v>
@@ -6042,13 +5122,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920032</v>
+        <v>21330051920050</v>
       </c>
       <c r="B24" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
         <v>163</v>
@@ -6059,13 +5139,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920033</v>
+        <v>21330051920049</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>164</v>
@@ -6076,13 +5156,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920034</v>
+        <v>21330051920051</v>
       </c>
       <c r="B26" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>165</v>
@@ -6093,13 +5173,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920040</v>
+        <v>21330051920052</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>166</v>
@@ -6110,13 +5190,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920041</v>
+        <v>21330051920053</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>167</v>
@@ -6127,13 +5207,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920042</v>
+        <v>21330051920054</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>168</v>
@@ -6144,13 +5224,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920044</v>
+        <v>21330051920055</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
         <v>169</v>
@@ -6161,13 +5241,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920046</v>
+        <v>21330051920056</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>170</v>
@@ -6178,13 +5258,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920047</v>
+        <v>21330051920057</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
         <v>171</v>
@@ -6195,13 +5275,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920048</v>
+        <v>21330051920058</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
         <v>172</v>
@@ -6212,13 +5292,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920050</v>
+        <v>21330051920059</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="D34" t="s">
         <v>173</v>
@@ -6229,13 +5309,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920049</v>
+        <v>21330051920060</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="D35" t="s">
         <v>174</v>
@@ -6246,13 +5326,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920051</v>
+        <v>21330051920061</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
         <v>175</v>
@@ -6263,13 +5343,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920055</v>
+        <v>21330051920062</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
         <v>176</v>
@@ -6280,13 +5360,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920056</v>
+        <v>21330051920063</v>
       </c>
       <c r="B38" t="s">
         <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D38" t="s">
         <v>177</v>
@@ -6297,13 +5377,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920058</v>
+        <v>21330051920064</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
         <v>178</v>
@@ -6314,13 +5394,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920059</v>
+        <v>21330051920065</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="D40" t="s">
         <v>179</v>
@@ -6331,16 +5411,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920060</v>
+        <v>21330051920066</v>
       </c>
       <c r="B41" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6348,16 +5428,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920063</v>
+        <v>21330051920067</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6365,16 +5445,16 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>21330051920064</v>
+        <v>21330051920069</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -6382,16 +5462,16 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44">
-        <v>21330051920065</v>
+        <v>20330051920185</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -6399,16 +5479,16 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>21330051920066</v>
+        <v>21330051920070</v>
       </c>
       <c r="B45" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D45" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -6421,7 +5501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6453,16 +5533,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920037</v>
+        <v>21330051920388</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6471,136 +5551,136 @@
         <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920037</v>
+        <v>21330051920388</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920390</v>
+        <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920390</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920043</v>
+        <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920043</v>
+        <v>21330051920039</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920067</v>
+        <v>21330051920052</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6609,44 +5689,44 @@
         <v>65</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920067</v>
+        <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920070</v>
+        <v>21330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6655,44 +5735,44 @@
         <v>65</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920070</v>
+        <v>21330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920030</v>
+        <v>21330051920065</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -6701,90 +5781,90 @@
         <v>65</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920035</v>
+        <v>21330051920067</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920038</v>
+        <v>21330051920069</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>66</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920045</v>
+        <v>20330051920185</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920054</v>
+        <v>21330051920070</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>183</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6793,30 +5873,7 @@
         <v>65</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920185</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
